--- a/out/MLP-S4_repeat_3_000006.xlsx
+++ b/out/MLP-S4_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>3.248249220197788</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.248249220197788</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>3.248249220197788</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>3.248249220197788</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.248249220197788</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.648249220197788</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.248249220197788</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.248249220197788</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.248249220197788</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.248249220197788</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.248249220197788</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004499999204052146</v>
+        <v>-0.0003128222096160753</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5791847404061293</v>
+        <v>0.4026263409910837</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.248249220197788</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.159465998829599</v>
+        <v>0.806015066578293</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.133757660132265</v>
+        <v>-0.09298306858678258</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3093304501946852</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.648249220197788</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3093304501946852</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.648249220197788</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4445100988518977</v>
+        <v>0.3090611464411744</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.434668166568933</v>
+        <v>0.8273593729251539</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.316703191631421</v>
+        <v>1.965427358179969</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2745075883289665</v>
+        <v>0.158305831513631</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.648249220197788</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.428956584300761</v>
+        <v>1.453472403560454</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4808260747334058</v>
+        <v>0.2772878948554011</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.648249220197788</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.116235706947391</v>
+        <v>1.849819837926228</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2633176178093107</v>
+        <v>0.1518529418944903</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>3.248249220197788</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.161630901769785</v>
+        <v>1.875998821448659</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.1087540109253835</v>
+        <v>0.06271747648045552</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.11554518384051</v>
+        <v>1.849421643296335</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1354981649726127</v>
+        <v>0.07814059364344086</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.648249220197788</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.27780634483379</v>
+        <v>1.94299588095038</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.08158798852459485</v>
+        <v>0.04705014038626072</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.305391226461587</v>
+        <v>1.958903724088574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.06202790641695657</v>
+        <v>0.03577165311867397</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.648249220197788</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.347825984689922</v>
+        <v>1.983375603149405</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02743510443087083</v>
+        <v>0.01582110087575931</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.340613372108505</v>
+        <v>1.979216191904165</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0217699619650522</v>
+        <v>0.01255309261819042</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.35670924501496</v>
+        <v>1.988497582471814</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01079389029668789</v>
+        <v>0.006223685855629567</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.648249220197788</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.35651149086833</v>
+        <v>1.988381415888184</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.006275964409814179</v>
+        <v>0.003616954928308779</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>3.248249220197788</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.358261322868989</v>
+        <v>1.989388350043265</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.003134027604534275</v>
+        <v>0.001804522863781575</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.35825241456772</v>
+        <v>1.989381097065147</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001547310007686119</v>
+        <v>0.0008890155785007095</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.358208119399129</v>
+        <v>1.989353431364695</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0008961662500337388</v>
+        <v>0.000515673833352827</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.648249220197788</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.35845232531287</v>
+        <v>1.989492417003745</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002963159653862076</v>
+        <v>0.0001690936688898088</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.358148053174766</v>
+        <v>1.989314504212841</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001454680068671599</v>
+        <v>8.258585474357068e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.358144731974035</v>
+        <v>1.989310473369611</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.817066842368922e-05</v>
+        <v>4.147772647206162e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.358153271645702</v>
+        <v>1.989313240302476</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.529306759837545e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.358145633439961</v>
+        <v>1.989306688416747</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.827360596503633e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.358149778817054</v>
+        <v>1.989307066984992</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.358141776992636</v>
+        <v>1.989300400021122</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.358138672307386</v>
+        <v>1.989296537946026</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.358134353316236</v>
+        <v>1.989291990633841</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.724541871943372e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.358129529143347</v>
+        <v>1.989292080578491</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.358128671209763</v>
+        <v>1.989291222644906</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.358128899530797</v>
+        <v>1.989291450965941</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.358128103866585</v>
+        <v>1.989290655301729</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.358128166135959</v>
+        <v>1.989290717571102</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.358128193811235</v>
+        <v>1.989290745246379</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.358128346025258</v>
+        <v>1.989290897460402</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.358128000084297</v>
+        <v>1.98929055151944</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.358128076191308</v>
+        <v>1.989290627626452</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.358128242242969</v>
+        <v>1.989290793678113</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.35812860202157</v>
+        <v>1.989291153456713</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.358128622778027</v>
+        <v>1.989291174213171</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.358128726560316</v>
+        <v>1.989291277995459</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.358128954881351</v>
+        <v>1.989291506316494</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.358128830342605</v>
+        <v>1.989291381777748</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.358128858017881</v>
+        <v>1.989291409453025</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.358128913368436</v>
+        <v>1.989291464803579</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.358129176283566</v>
+        <v>1.989291727718709</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.358129093257736</v>
+        <v>1.989291644692879</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.358128885693159</v>
+        <v>1.989291437128302</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.358128899530797</v>
+        <v>1.989291450965941</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.358129037907181</v>
+        <v>1.989291589342325</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.358128754235594</v>
+        <v>1.989291305670736</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.358128581265112</v>
+        <v>1.989291132700256</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.358128477482824</v>
+        <v>1.989291028917967</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.358128622778027</v>
+        <v>1.989291174213171</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.358128864936701</v>
+        <v>1.989291416371844</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.35812869196622</v>
+        <v>1.989291243401363</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.358128394456993</v>
+        <v>1.989290945892137</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.358128380619354</v>
+        <v>1.989290932054498</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.358128013921935</v>
+        <v>1.989290565357078</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.358128013921935</v>
+        <v>1.989290565357078</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.358127951652562</v>
+        <v>1.989290503087705</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.358127847870274</v>
+        <v>1.989290399305417</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.358127674899793</v>
+        <v>1.989290226334936</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.358127723331528</v>
+        <v>1.989290274766671</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.358127363552927</v>
+        <v>1.989289914988071</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.358127322040012</v>
+        <v>1.989289873475155</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.358127377390566</v>
+        <v>1.989289928825709</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.358127432741119</v>
+        <v>1.989289984176263</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.358127474254035</v>
+        <v>1.989290025689179</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.358127204420085</v>
+        <v>1.989289755855228</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.358127259770639</v>
+        <v>1.989289811205782</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.358127405065843</v>
+        <v>1.989289956500986</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.358127370471747</v>
+        <v>1.98928992190689</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.358127356634109</v>
+        <v>1.989289908069252</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.358127446578758</v>
+        <v>1.989289998013902</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>3.248249220197788</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.358127764844443</v>
+        <v>1.989290316279586</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.358127584955143</v>
+        <v>1.989290136390286</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.358127626468059</v>
+        <v>1.989290177903202</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.358127439659939</v>
+        <v>1.989289991095082</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.358127508848132</v>
+        <v>1.989290060283274</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.358127308202374</v>
+        <v>1.989289859637517</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.358127349715289</v>
+        <v>1.989289901150432</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.358127377390566</v>
+        <v>1.989289928825709</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_3_000006.xlsx
+++ b/out/MLP-S4_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>3.248249220197788</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307028</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.248249220197788</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307027</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307028</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.648249220197788</v>
+        <v>0.3299763727307028</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307027</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.3299763727307027</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.248249220197788</v>
+        <v>0.5299763727307027</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307027</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307027</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004499999204052146</v>
+        <v>-0.0003504305209416197</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5791847404061293</v>
+        <v>0.4510313776757547</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.159465998829599</v>
+        <v>0.9029163236767631</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.133757660132265</v>
+        <v>-0.1041616839519103</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3465192632029026</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.648249220197788</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3465192632029026</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.648249220197788</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4445100988518977</v>
+        <v>0.3462534548566006</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.434668166568933</v>
+        <v>0.8166207260303577</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.316703191631421</v>
+        <v>1.981120989649913</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2745075883289665</v>
+        <v>0.1562511745264073</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.648249220197788</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.428956584300761</v>
+        <v>1.475810914538187</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4808260747334058</v>
+        <v>0.273688533209207</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.648249220197788</v>
+        <v>1.981656608135626</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.116235706947391</v>
+        <v>1.867013835033815</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2633176178093107</v>
+        <v>0.1498820387361072</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.161630901769785</v>
+        <v>1.892853040869599</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.1087540109253835</v>
+        <v>0.06190346477321424</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.11554518384051</v>
+        <v>1.866620808582056</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1354981649726127</v>
+        <v>0.07712640490999643</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.648249220197788</v>
+        <v>0.3299763727307026</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.27780634483379</v>
+        <v>1.958980543848233</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.08158798852459485</v>
+        <v>0.04643946776356856</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.305391226461587</v>
+        <v>1.974681918702126</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.06202790641695657</v>
+        <v>0.03530647974127091</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.648249220197788</v>
+        <v>0.3299763727307026</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.347825984689922</v>
+        <v>1.998836182043328</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02743510443087083</v>
+        <v>0.01561614787184558</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307027</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.340613372108505</v>
+        <v>1.994730650821667</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0217699619650522</v>
+        <v>0.01239167106214218</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307027</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.35670924501496</v>
+        <v>2.003891752213606</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01079389029668789</v>
+        <v>0.0061411370069405</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.648249220197788</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.35651149086833</v>
+        <v>2.003777038165591</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.006275964409814179</v>
+        <v>0.003570407716378706</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>3.248249220197788</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.358261322868989</v>
+        <v>2.004770967544382</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.003134027604534275</v>
+        <v>0.001781249257816538</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.35825241456772</v>
+        <v>2.004763743543475</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001547310007686119</v>
+        <v>0.0008775169858511826</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307026</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.358208119399129</v>
+        <v>2.004736368918346</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0008961662500337388</v>
+        <v>0.0005089985277970213</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.648249220197788</v>
+        <v>0.3299763727307026</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.35845232531287</v>
+        <v>2.004873508587665</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002963159653862076</v>
+        <v>0.0001668616987758369</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307026</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.358148053174766</v>
+        <v>2.004697812627413</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001454680068671599</v>
+        <v>8.034006359629965e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.358144731974035</v>
+        <v>2.004693770771648</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.817066842368922e-05</v>
+        <v>4.147772647206162e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.358153271645702</v>
+        <v>2.004696537704514</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.529306759837545e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.358145633439961</v>
+        <v>2.004689985818785</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.827360596503633e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.358149778817054</v>
+        <v>2.00469036438703</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.358141776992636</v>
+        <v>2.004683697423159</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.358138672307386</v>
+        <v>2.004679835348063</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.358134353316236</v>
+        <v>2.004675288035878</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.724541871943372e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.358129529143347</v>
+        <v>2.004675377980528</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.358128671209763</v>
+        <v>2.004674520046943</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.358128899530797</v>
+        <v>2.004674748367978</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.358128103866585</v>
+        <v>2.004673952703766</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.358128166135959</v>
+        <v>2.004674014973139</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.358128193811235</v>
+        <v>2.004674042648416</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.358128346025258</v>
+        <v>2.004674194862439</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.358128000084297</v>
+        <v>2.004673848921477</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.358128076191308</v>
+        <v>2.004673925028489</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.358128242242969</v>
+        <v>2.004674091080151</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.35812860202157</v>
+        <v>2.00467445085875</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.358128622778027</v>
+        <v>2.004674471615208</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.358128726560316</v>
+        <v>2.004674575397496</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.358128954881351</v>
+        <v>2.004674803718531</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.358128830342605</v>
+        <v>2.004674679179785</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.358128858017881</v>
+        <v>2.004674706855063</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.358128913368436</v>
+        <v>2.004674762205616</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.358129176283566</v>
+        <v>2.004675025120747</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.358129093257736</v>
+        <v>2.004674942094916</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.358128885693159</v>
+        <v>2.004674734530339</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.358128899530797</v>
+        <v>2.004674748367978</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.358129037907181</v>
+        <v>2.004674886744362</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.358128754235594</v>
+        <v>2.004674603072774</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.358128581265112</v>
+        <v>2.004674430102293</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.358128477482824</v>
+        <v>2.004674326320005</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.358128622778027</v>
+        <v>2.004674471615208</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.358128864936701</v>
+        <v>2.004674713773881</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.35812869196622</v>
+        <v>2.004674540803401</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.358128394456993</v>
+        <v>2.004674243294174</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.358128380619354</v>
+        <v>2.004674229456535</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.358128013921935</v>
+        <v>2.004673862759116</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.358128013921935</v>
+        <v>2.004673862759116</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.358127951652562</v>
+        <v>2.004673800489743</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.358127847870274</v>
+        <v>2.004673696707454</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.358127674899793</v>
+        <v>2.004673523736973</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.358127723331528</v>
+        <v>2.004673572168708</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.358127363552927</v>
+        <v>2.004673212390108</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.358127322040012</v>
+        <v>2.004673170877193</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.358127377390566</v>
+        <v>2.004673226227746</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.358127432741119</v>
+        <v>2.004673281578301</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.358127474254035</v>
+        <v>2.004673323091216</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.358127204420085</v>
+        <v>2.004673053257266</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.358127259770639</v>
+        <v>2.004673108607819</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.358127405065843</v>
+        <v>2.004673253903023</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.358127370471747</v>
+        <v>2.004673219308927</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.358127356634109</v>
+        <v>2.004673205471289</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.358127446578758</v>
+        <v>2.004673295415939</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>3.248249220197788</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.358127764844443</v>
+        <v>2.004673613681623</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.358127584955143</v>
+        <v>2.004673433792323</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.358127626468059</v>
+        <v>2.004673475305239</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.358127439659939</v>
+        <v>2.004673288497119</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.358127508848132</v>
+        <v>2.004673357685312</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.358127308202374</v>
+        <v>2.004673157039554</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.358127349715289</v>
+        <v>2.00467319855247</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.358127377390566</v>
+        <v>2.004673226227746</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_3_000006.xlsx
+++ b/out/MLP-S4_repeat_3_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4067746698856354</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4143589735031128</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4443727731704712</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4806166589260101</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4312120676040649</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4630147218704224</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4156854152679443</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4820584058761597</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4891272783279419</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4392995536327362</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4150366187095642</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4020468592643738</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4657793641090393</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4250412881374359</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4174772799015045</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4190627932548523</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4509645104408264</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4808899760246277</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.5305454134941101</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4754195213317871</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4577168524265289</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.2958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4375958442687988</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.2958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4408195316791534</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.3299763727307028</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5075365304946899</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5299763727307029</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4444119930267334</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.355816490433164</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.5365814566612244</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.355816490433164</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.660971462726593</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.181656608135626</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5610937476158142</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.355816490433165</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4859998524188995</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5299763727307027</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.499491423368454</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4414103925228119</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4163845181465149</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4442696869373322</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3299763727307028</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5783128142356873</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3299763727307028</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4968304038047791</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3299763727307027</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4814020693302155</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.3299763727307027</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5219680070877075</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5299763727307027</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4536185264587402</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.5299763727307027</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4717898368835449</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5299763727307027</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5248205661773682</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.355816490433164</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5848926901817322</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.181656608135626</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6170309782028198</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.181656608135626</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6969830393791199</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.181656608135626</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003504305209416197</v>
+        <v>-0.0001826481971237809</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4510313776757547</v>
+        <v>0.2350824573080914</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6439861059188843</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.355816490433164</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9029163236767631</v>
+        <v>0.4706098037066381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1041616839519103</v>
+        <v>-0.05429020204081502</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.4902714788913727</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.355816490433164</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3465192632029026</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5393055081367493</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3465192632029026</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5286288261413574</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3462534548566006</v>
+        <v>0.1805492523242068</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8166207260303577</v>
+        <v>0.1854226701566546</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4585809111595154</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.981120989649913</v>
+        <v>0.5517641376967581</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1562511745264073</v>
+        <v>0.0354786007527919</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5752600431442261</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.16</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.475810914538187</v>
+        <v>0.4370277559345695</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.273688533209207</v>
+        <v>0.06214413394122734</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.543431282043457</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.981656608135626</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.867013835033815</v>
+        <v>0.5258548144014841</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1498820387361072</v>
+        <v>0.03403238920826912</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.542854905128479</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.355816490433164</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.892853040869599</v>
+        <v>0.5317218943881942</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06190346477321424</v>
+        <v>0.01405587236647913</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4751968383789062</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.355816490433164</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.866620808582056</v>
+        <v>0.5257655733604077</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07712640490999643</v>
+        <v>0.01751192035485199</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.6384652853012085</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.3299763727307026</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.958980543848233</v>
+        <v>0.5467368825751256</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04643946776356856</v>
+        <v>0.01054288952356224</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4625447392463684</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.155816490433164</v>
+        <v>0.16</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.974681918702126</v>
+        <v>0.5503006069246938</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03530647974127091</v>
+        <v>0.008015056170379379</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.685381293296814</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.3299763727307026</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.998836182043328</v>
+        <v>0.5557830431526014</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01561614787184558</v>
+        <v>0.003542299890334637</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3481892645359039</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3299763727307027</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.994730650821667</v>
+        <v>0.5548469297300284</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01239167106214218</v>
+        <v>0.002809788383591186</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.2610600292682648</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.3299763727307027</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.003891752213606</v>
+        <v>0.5569231848985744</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0061411370069405</v>
+        <v>0.001390825986924216</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.7978905439376831</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.003777038165591</v>
+        <v>0.5568932728689899</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003570407716378706</v>
+        <v>0.0008066670080306419</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.7351762056350708</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.004770967544382</v>
+        <v>0.5571150436555501</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001781249257816538</v>
+        <v>0.0003993789036425062</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.4967839419841766</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5299763727307025</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.004763743543475</v>
+        <v>0.5571095401765174</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0008775169858511826</v>
+        <v>0.0001962253713667192</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4699760377407074</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.3299763727307026</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.004736368918346</v>
+        <v>0.5570994463583666</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005089985277970213</v>
+        <v>0.0001118178472265958</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.5026127696037292</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.3299763727307026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.004873508587665</v>
+        <v>0.5571267508286664</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001668616987758369</v>
+        <v>3.294349193752244e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.310696005821228</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.3299763727307026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.004697812627413</v>
+        <v>0.5570829576964944</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.034006359629965e-05</v>
+        <v>1.521212032543939e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.3186062872409821</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.004693770771648</v>
+        <v>0.5570781813480568</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.147772647206162e-05</v>
+        <v>4.784784520434025e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.3308517932891846</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.004696537704514</v>
+        <v>0.5570749748963635</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.3430001139640808</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.004689985818785</v>
+        <v>0.5570695884122059</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4380984902381897</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.00469036438703</v>
+        <v>0.557066203793755</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.4017665684223175</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.004683697423159</v>
+        <v>0.5570605363634813</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4217245876789093</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.004679835348063</v>
+        <v>0.5570609168985391</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3415689468383789</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.004675288035878</v>
+        <v>0.5570611452195737</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.2956794798374176</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.004675377980528</v>
+        <v>0.5570612351642237</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2928304374217987</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.004674520046943</v>
+        <v>0.5570603772306388</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3239799439907074</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.004674748367978</v>
+        <v>0.5570606055516736</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.2975040972232819</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.004673952703766</v>
+        <v>0.5570598098874618</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.1910747736692429</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.004674014973139</v>
+        <v>0.5570598721568349</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.2559456527233124</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.004674042648416</v>
+        <v>0.5570598998321118</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3427986800670624</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.004674194862439</v>
+        <v>0.5570600520461351</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2054198682308197</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.004673848921477</v>
+        <v>0.5570597061051733</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.2963318824768066</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.004673925028489</v>
+        <v>0.557059782212185</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.2591888606548309</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.004674091080151</v>
+        <v>0.5570599482638465</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.422447681427002</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.00467445085875</v>
+        <v>0.5570603080424467</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4292520880699158</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.004674471615208</v>
+        <v>0.5570603287989043</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4713177084922791</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.004674575397496</v>
+        <v>0.5570604325811929</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.3628516793251038</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.004674803718531</v>
+        <v>0.5570606609022275</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.2804679572582245</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.004674679179785</v>
+        <v>0.5570605363634813</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3124150931835175</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.004674706855063</v>
+        <v>0.5570605640387581</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.387338399887085</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.004674762205616</v>
+        <v>0.5570606193893121</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3477300405502319</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.004675025120747</v>
+        <v>0.5570608823044428</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.337136298418045</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.004674942094916</v>
+        <v>0.557060799278612</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3030682802200317</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.004674734530339</v>
+        <v>0.5570605917140352</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.3503773808479309</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.004674748367978</v>
+        <v>0.5570606055516736</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3208537995815277</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.004674886744362</v>
+        <v>0.5570607439280583</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3187595009803772</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.004674603072774</v>
+        <v>0.5570604602564697</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.2840246260166168</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.004674430102293</v>
+        <v>0.5570602872859889</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3810073435306549</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.004674326320005</v>
+        <v>0.5570601835037005</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3678874671459198</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.004674471615208</v>
+        <v>0.5570603287989043</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3033750057220459</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.004674713773881</v>
+        <v>0.5570605709575775</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3129171431064606</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.004674540803401</v>
+        <v>0.5570603979870966</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3116980493068695</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.004674243294174</v>
+        <v>0.5570601004778696</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3191280663013458</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.004674229456535</v>
+        <v>0.5570600866402311</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3048072755336761</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.004673862759116</v>
+        <v>0.5570597199428119</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3573991060256958</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.004673862759116</v>
+        <v>0.5570597199428119</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.3951659798622131</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.004673800489743</v>
+        <v>0.5570596576734388</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3129051029682159</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.004673696707454</v>
+        <v>0.5570595538911502</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3429180085659027</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.004673523736973</v>
+        <v>0.5570593809206695</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3496701121330261</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.004673572168708</v>
+        <v>0.557059429352404</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3120189309120178</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.004673212390108</v>
+        <v>0.557059069573804</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3167193233966827</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.004673170877193</v>
+        <v>0.5570590280608886</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3739056885242462</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.004673226227746</v>
+        <v>0.5570590834114424</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3385891914367676</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.004673281578301</v>
+        <v>0.5570591387619963</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.352119654417038</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.004673323091216</v>
+        <v>0.5570591802749116</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3439413011074066</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.004673053257266</v>
+        <v>0.5570589104409616</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3839689493179321</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.004673108607819</v>
+        <v>0.5570589657915156</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3775864839553833</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.004673253903023</v>
+        <v>0.5570591110867195</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3794362246990204</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.004673219308927</v>
+        <v>0.5570590764926232</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3629822432994843</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.004673205471289</v>
+        <v>0.5570590626549846</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4659831523895264</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.004673295415939</v>
+        <v>0.5570591525996348</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.5854806900024414</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.004673613681623</v>
+        <v>0.5570594708653195</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4236354827880859</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.004673433792323</v>
+        <v>0.5570592909760194</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3854484558105469</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.2958637449717587</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.004673475305239</v>
+        <v>0.5570593324889347</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4011517465114594</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.2958637449717587</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.004673288497119</v>
+        <v>0.5570591456808155</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3312757611274719</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.004673357685312</v>
+        <v>0.5570592148690079</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3596328794956207</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.004673157039554</v>
+        <v>0.5570590142232501</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3477207720279694</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5800000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.00467319855247</v>
+        <v>0.5570590557361655</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.3805263638496399</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7200000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.004673226227746</v>
+        <v>0.5570590834114424</v>
       </c>
     </row>
   </sheetData>
